--- a/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
+++ b/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\TT ODD 2026\TT_3Aug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fileserver2\time table\JIIT Time Table Odd 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9CCE91-FCB9-4A01-857F-120CD02BD23F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227FBE72-0D7A-4113-B053-F537596FAE14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>PB5-B9(16CS312)-CL17/MSH</t>
   </si>
   <si>
-    <t>LB5,B6(HS311)-CS3 /IJ</t>
-  </si>
-  <si>
     <t>LC1,C2,C3 (HS311)- CS3/YN</t>
   </si>
   <si>
@@ -344,9 +341,6 @@
     <t>LA17-A18(24B31EC311)-CS2/ABU</t>
   </si>
   <si>
-    <t>LA15-A16(25HS311)-CS4/MSU</t>
-  </si>
-  <si>
     <t>LA1-A2(EC312)-G6/VNS</t>
   </si>
   <si>
@@ -666,9 +660,6 @@
     <t>LC1-C3(BT413)- CS3/ASM,AKV</t>
   </si>
   <si>
-    <t>LA15-A16(25HS311)-CS1/MSU</t>
-  </si>
-  <si>
     <t>LA15,A16(HS311)-F8 /NAM</t>
   </si>
   <si>
@@ -1549,6 +1540,36 @@
   </si>
   <si>
     <t>PB1-B9(16CS320)-CL02,03/ASK,TRN,SAM</t>
+  </si>
+  <si>
+    <t>LB5,B6(HS311)-G2 /IJ,NAM</t>
+  </si>
+  <si>
+    <t>LA15-A16(24B21EC311)-F6/RSB</t>
+  </si>
+  <si>
+    <r>
+      <t>LA15-A16(25HS311)-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>LT2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/MSU</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2055,7 +2076,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2412,6 +2433,90 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2460,95 +2565,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2878,19 +2902,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33" customHeight="1">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="171"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="131"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2"/>
@@ -2952,20 +2976,20 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.25" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="148" t="s">
+      <c r="B5" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="148"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="138" t="s">
+      <c r="F5" s="166" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -2977,13 +3001,13 @@
       <c r="I5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="148" t="s">
+      <c r="J5" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="148"/>
+      <c r="K5" s="132"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A6" s="130"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
         <v>20</v>
@@ -2994,7 +3018,7 @@
       <c r="E6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="139"/>
+      <c r="F6" s="167"/>
       <c r="G6" s="8" t="s">
         <v>23</v>
       </c>
@@ -3010,7 +3034,7 @@
       <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A7" s="130"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>27</v>
@@ -3019,9 +3043,9 @@
         <v>28</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7" s="139"/>
+        <v>242</v>
+      </c>
+      <c r="F7" s="167"/>
       <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
@@ -3035,254 +3059,251 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A8" s="130"/>
-      <c r="B8" s="149" t="s">
+      <c r="A8" s="158"/>
+      <c r="B8" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="149"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="133"/>
+      <c r="E8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="167"/>
+      <c r="G8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="139"/>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="130"/>
-      <c r="B9" s="148" t="s">
+      <c r="A9" s="158"/>
+      <c r="B9" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="132"/>
+      <c r="D9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="148"/>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="167"/>
+      <c r="H9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="139"/>
-      <c r="H9" s="13" t="s">
-        <v>41</v>
-      </c>
       <c r="I9" s="8" t="s">
-        <v>42</v>
+        <v>507</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A10" s="130"/>
-      <c r="B10" s="148" t="s">
+      <c r="A10" s="158"/>
+      <c r="B10" s="132" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="132"/>
+      <c r="D10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="148"/>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="139"/>
+      <c r="F10" s="167"/>
       <c r="G10" s="9"/>
       <c r="H10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A11" s="130"/>
-      <c r="B11" s="148" t="s">
+      <c r="A11" s="158"/>
+      <c r="B11" s="132" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="132"/>
+      <c r="D11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="148"/>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="139"/>
-      <c r="G11" s="149" t="s">
-        <v>504</v>
-      </c>
-      <c r="H11" s="149"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="133" t="s">
+        <v>501</v>
+      </c>
+      <c r="H11" s="133"/>
       <c r="I11" s="109"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A12" s="130"/>
-      <c r="B12" s="148" t="s">
+      <c r="A12" s="158"/>
+      <c r="B12" s="132" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="132"/>
+      <c r="D12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="148"/>
-      <c r="D12" s="13" t="s">
+      <c r="E12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="F12" s="167"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="139"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="167" t="s">
+      <c r="J12" s="137"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A13" s="158"/>
+      <c r="B13" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="168"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="130"/>
-      <c r="B13" s="148" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="148"/>
+      <c r="C13" s="132"/>
       <c r="D13" s="109"/>
       <c r="E13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="167"/>
+      <c r="G13" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="139"/>
-      <c r="G13" s="167" t="s">
+      <c r="H13" s="137"/>
+      <c r="I13" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="168"/>
-      <c r="I13" s="167" t="s">
+      <c r="J13" s="137"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A14" s="158"/>
+      <c r="B14" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="168"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A14" s="130"/>
-      <c r="B14" s="148" t="s">
+      <c r="C14" s="132"/>
+      <c r="D14" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="148"/>
-      <c r="D14" s="13" t="s">
+      <c r="E14" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="167"/>
+      <c r="G14" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="139"/>
-      <c r="G14" s="146" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="147"/>
+      <c r="H14" s="139"/>
       <c r="I14" s="16"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A15" s="130"/>
-      <c r="B15" s="148" t="s">
+      <c r="A15" s="158"/>
+      <c r="B15" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="132"/>
+      <c r="D15" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="148"/>
-      <c r="D15" s="146" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="147"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="147"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="167"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="139"/>
       <c r="I15" s="17"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A16" s="130"/>
-      <c r="B16" s="148" t="s">
+      <c r="A16" s="158"/>
+      <c r="B16" s="132" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="132"/>
+      <c r="D16" s="133" t="s">
+        <v>500</v>
+      </c>
+      <c r="E16" s="133"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="148"/>
-      <c r="D16" s="149" t="s">
-        <v>503</v>
-      </c>
-      <c r="E16" s="149"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" s="148"/>
+      <c r="I16" s="132"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A17" s="130"/>
+      <c r="A17" s="158"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
-      <c r="D17" s="146"/>
-      <c r="E17" s="147"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="139"/>
       <c r="F17" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="148"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A18" s="130"/>
+      <c r="A18" s="158"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
-      <c r="D18" s="154" t="s">
+      <c r="D18" s="140" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="140"/>
+      <c r="F18" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="154"/>
-      <c r="F18" s="19" t="s">
+      <c r="G18" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="148" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="148"/>
+      <c r="H18" s="132"/>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
-      <c r="A19" s="130"/>
+      <c r="A19" s="158"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="148" t="s">
+      <c r="D19" s="132" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="132"/>
+      <c r="F19" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="148"/>
-      <c r="F19" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="148"/>
-      <c r="H19" s="148"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="132"/>
       <c r="I19" s="16"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A20" s="131"/>
+      <c r="A20" s="159"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="148" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="148"/>
+      <c r="D20" s="132" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="132"/>
       <c r="F20" s="21"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
@@ -3304,19 +3325,19 @@
       <c r="K21" s="26"/>
     </row>
     <row r="22" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A22" s="132" t="s">
+      <c r="A22" s="160" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="C22" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>14</v>
@@ -3325,25 +3346,25 @@
         <v>17</v>
       </c>
       <c r="I22" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" customHeight="1">
+      <c r="A23" s="161"/>
+      <c r="B23" s="42" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="30" customHeight="1">
-      <c r="A23" s="133"/>
-      <c r="B23" s="42" t="s">
+      <c r="C23" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="19" t="s">
         <v>82</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>83</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>22</v>
@@ -3352,29 +3373,29 @@
         <v>24</v>
       </c>
       <c r="I23" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="109"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1">
+      <c r="A24" s="161"/>
+      <c r="B24" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="109"/>
-    </row>
-    <row r="24" spans="1:11" ht="30" customHeight="1">
-      <c r="A24" s="133"/>
-      <c r="B24" s="42" t="s">
+      <c r="C24" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="G24" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>28</v>
@@ -3386,125 +3407,125 @@
       <c r="K24" s="30"/>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
-      <c r="A25" s="133"/>
+      <c r="A25" s="161"/>
       <c r="B25" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="G25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="I25" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>97</v>
       </c>
       <c r="J25" s="31"/>
       <c r="K25" s="30"/>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
-      <c r="A26" s="133"/>
+      <c r="A26" s="161"/>
       <c r="B26" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="169" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="141" t="s">
+      <c r="G26" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="H26" s="109"/>
       <c r="I26" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J26" s="31"/>
       <c r="K26" s="30"/>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
-      <c r="A27" s="133"/>
+      <c r="A27" s="161"/>
       <c r="B27" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="D27" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="E27" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="F27" s="170"/>
+      <c r="G27" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="142"/>
-      <c r="G27" s="8" t="s">
+      <c r="I27" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="J27" s="31"/>
       <c r="K27" s="30"/>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
-      <c r="A28" s="133"/>
+      <c r="A28" s="161"/>
       <c r="B28" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="F28" s="170"/>
+      <c r="G28" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="H28" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="F28" s="142"/>
-      <c r="G28" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>116</v>
       </c>
       <c r="I28" s="109"/>
       <c r="J28" s="31"/>
       <c r="K28" s="30"/>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
-      <c r="A29" s="133"/>
+      <c r="A29" s="161"/>
       <c r="B29" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="E29" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="142"/>
+      <c r="F29" s="170"/>
       <c r="G29" s="109"/>
       <c r="H29" s="18"/>
       <c r="I29" s="9"/>
@@ -3512,20 +3533,20 @@
       <c r="K29" s="30"/>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1">
-      <c r="A30" s="133"/>
+      <c r="A30" s="161"/>
       <c r="B30" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="E30" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="142"/>
+      <c r="F30" s="170"/>
       <c r="G30" s="109"/>
       <c r="H30" s="18"/>
       <c r="I30" s="9"/>
@@ -3533,79 +3554,79 @@
       <c r="K30" s="30"/>
     </row>
     <row r="31" spans="1:11" ht="30" customHeight="1">
-      <c r="A31" s="133"/>
+      <c r="A31" s="161"/>
       <c r="B31" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="E31" s="109"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="132" t="s">
         <v>126</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="109"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="148" t="s">
-        <v>128</v>
-      </c>
-      <c r="I31" s="148"/>
+      <c r="I31" s="132"/>
       <c r="J31" s="31"/>
       <c r="K31" s="30"/>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1">
-      <c r="A32" s="133"/>
+      <c r="A32" s="161"/>
       <c r="B32" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="E32" s="18"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="140" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="154" t="s">
-        <v>132</v>
-      </c>
-      <c r="H32" s="154"/>
+      <c r="H32" s="140"/>
       <c r="I32" s="18"/>
       <c r="J32" s="31"/>
       <c r="K32" s="30"/>
     </row>
     <row r="33" spans="1:11" ht="30" customHeight="1">
-      <c r="A33" s="133"/>
+      <c r="A33" s="161"/>
       <c r="B33" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="E33" s="18"/>
+      <c r="F33" s="170"/>
+      <c r="G33" s="140" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="H33" s="154"/>
+      <c r="H33" s="140"/>
       <c r="I33" s="30"/>
       <c r="J33" s="31"/>
       <c r="K33" s="30"/>
     </row>
     <row r="34" spans="1:11" ht="27" customHeight="1">
-      <c r="A34" s="133"/>
+      <c r="A34" s="161"/>
       <c r="B34" s="110"/>
       <c r="C34" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="154" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="154"/>
-      <c r="F34" s="142"/>
+        <v>135</v>
+      </c>
+      <c r="D34" s="140" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="140"/>
+      <c r="F34" s="170"/>
       <c r="G34" s="109"/>
       <c r="H34" s="109"/>
       <c r="I34" s="30"/>
@@ -3613,38 +3634,38 @@
       <c r="K34" s="30"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="133"/>
+      <c r="A35" s="161"/>
       <c r="B35" s="110"/>
       <c r="C35" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="163" t="s">
-        <v>140</v>
-      </c>
-      <c r="H35" s="163"/>
+      <c r="F35" s="170"/>
+      <c r="G35" s="141" t="s">
+        <v>138</v>
+      </c>
+      <c r="H35" s="141"/>
       <c r="I35" s="18"/>
       <c r="J35" s="31"/>
       <c r="K35" s="30"/>
     </row>
     <row r="36" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A36" s="134"/>
+      <c r="A36" s="162"/>
       <c r="B36" s="42"/>
       <c r="C36" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="132" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" s="132"/>
+      <c r="F36" s="170"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="140" t="s">
         <v>141</v>
       </c>
-      <c r="D36" s="148" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="148"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="154" t="s">
-        <v>143</v>
-      </c>
-      <c r="I36" s="154"/>
+      <c r="I36" s="140"/>
       <c r="J36" s="15"/>
       <c r="K36" s="8"/>
     </row>
@@ -3652,14 +3673,14 @@
       <c r="A37" s="28"/>
       <c r="B37" s="111"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="148"/>
-      <c r="E37" s="148"/>
-      <c r="F37" s="142"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="170"/>
       <c r="G37" s="16"/>
-      <c r="H37" s="161" t="s">
-        <v>144</v>
-      </c>
-      <c r="I37" s="161"/>
+      <c r="H37" s="142" t="s">
+        <v>142</v>
+      </c>
+      <c r="I37" s="142"/>
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
     </row>
@@ -3667,16 +3688,16 @@
       <c r="A38" s="28"/>
       <c r="B38" s="111"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="148" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" s="148"/>
-      <c r="F38" s="142"/>
+      <c r="D38" s="132" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="132"/>
+      <c r="F38" s="170"/>
       <c r="G38" s="9"/>
-      <c r="H38" s="148" t="s">
-        <v>146</v>
-      </c>
-      <c r="I38" s="148"/>
+      <c r="H38" s="132" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" s="132"/>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
@@ -3684,16 +3705,16 @@
       <c r="A39" s="28"/>
       <c r="B39" s="112"/>
       <c r="C39" s="34"/>
-      <c r="D39" s="164" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="165"/>
-      <c r="F39" s="143"/>
+      <c r="D39" s="144" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" s="145"/>
+      <c r="F39" s="171"/>
       <c r="G39" s="21"/>
-      <c r="H39" s="146" t="s">
-        <v>148</v>
-      </c>
-      <c r="I39" s="147"/>
+      <c r="H39" s="138" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" s="139"/>
       <c r="J39" s="15"/>
       <c r="K39" s="15"/>
     </row>
@@ -3701,10 +3722,10 @@
       <c r="A40" s="28"/>
       <c r="B40" s="6"/>
       <c r="C40" s="35"/>
-      <c r="D40" s="146" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="166"/>
+      <c r="D40" s="138" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="146"/>
       <c r="F40" s="27"/>
       <c r="G40" s="27"/>
       <c r="J40" s="36"/>
@@ -3724,14 +3745,14 @@
       <c r="K41" s="26"/>
     </row>
     <row r="42" spans="1:11" ht="25.5">
-      <c r="A42" s="135" t="s">
+      <c r="A42" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="B42" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>14</v>
@@ -3739,28 +3760,28 @@
       <c r="E42" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F42" s="144" t="s">
-        <v>77</v>
+      <c r="F42" s="154" t="s">
+        <v>76</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H42" s="148" t="s">
+      <c r="H42" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="I42" s="148"/>
-      <c r="J42" s="162" t="s">
+      <c r="I42" s="132"/>
+      <c r="J42" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="K42" s="147"/>
+      <c r="K42" s="139"/>
     </row>
     <row r="43" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A43" s="135"/>
+      <c r="A43" s="163"/>
       <c r="B43" s="39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>22</v>
@@ -3768,122 +3789,122 @@
       <c r="E43" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="144"/>
+      <c r="F43" s="154"/>
       <c r="G43" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H43" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J43" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="K43" s="8"/>
+    </row>
+    <row r="44" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A44" s="163"/>
+      <c r="B44" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="C44" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="K43" s="8"/>
-    </row>
-    <row r="44" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A44" s="135"/>
-      <c r="B44" s="39" t="s">
+      <c r="D44" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="E44" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D44" s="40" t="s">
+      <c r="F44" s="154"/>
+      <c r="G44" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="H44" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="F44" s="144"/>
-      <c r="G44" s="11" t="s">
+      <c r="I44" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>164</v>
       </c>
       <c r="J44" s="15"/>
       <c r="K44" s="8"/>
     </row>
     <row r="45" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A45" s="135"/>
+      <c r="A45" s="163"/>
       <c r="B45" s="41"/>
       <c r="C45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="F45" s="154"/>
+      <c r="G45" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="H45" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="144"/>
-      <c r="G45" s="8" t="s">
+      <c r="I45" s="13" t="s">
         <v>168</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>170</v>
       </c>
       <c r="J45" s="15"/>
       <c r="K45" s="8"/>
     </row>
     <row r="46" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A46" s="135"/>
+      <c r="A46" s="163"/>
       <c r="B46" s="41"/>
       <c r="C46" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D46" s="42"/>
       <c r="E46" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F46" s="144"/>
+        <v>170</v>
+      </c>
+      <c r="F46" s="154"/>
       <c r="G46" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
     </row>
     <row r="47" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A47" s="135"/>
+      <c r="A47" s="163"/>
       <c r="B47" s="41"/>
       <c r="C47" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F47" s="144"/>
+      <c r="F47" s="154"/>
       <c r="G47" s="127" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
     </row>
     <row r="48" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A48" s="135"/>
+      <c r="A48" s="163"/>
       <c r="B48" s="43"/>
       <c r="C48" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F48" s="144"/>
+      <c r="F48" s="154"/>
       <c r="G48" s="109"/>
       <c r="H48" s="9"/>
       <c r="I48" s="16"/>
@@ -3891,37 +3912,37 @@
       <c r="K48" s="8"/>
     </row>
     <row r="49" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A49" s="135"/>
+      <c r="A49" s="163"/>
       <c r="B49" s="44"/>
       <c r="C49" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="E49" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="F49" s="154"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="140" t="s">
         <v>181</v>
       </c>
-      <c r="E49" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="F49" s="144"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="154" t="s">
-        <v>183</v>
-      </c>
-      <c r="I49" s="154"/>
+      <c r="I49" s="140"/>
       <c r="J49" s="15"/>
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A50" s="135"/>
+      <c r="A50" s="163"/>
       <c r="B50" s="44"/>
       <c r="C50" s="8"/>
       <c r="D50" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="F50" s="144"/>
+        <v>183</v>
+      </c>
+      <c r="F50" s="154"/>
       <c r="G50" s="18"/>
       <c r="H50" s="17"/>
       <c r="I50" s="17"/>
@@ -3929,96 +3950,98 @@
       <c r="K50" s="8"/>
     </row>
     <row r="51" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A51" s="135"/>
+      <c r="A51" s="163"/>
       <c r="B51" s="44"/>
       <c r="C51" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="147" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="147"/>
+      <c r="F51" s="154"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="D51" s="156" t="s">
-        <v>187</v>
-      </c>
-      <c r="E51" s="156"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="148" t="s">
-        <v>188</v>
-      </c>
-      <c r="I51" s="148"/>
+      <c r="I51" s="132"/>
       <c r="J51" s="15"/>
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A52" s="135"/>
+      <c r="A52" s="163"/>
       <c r="B52" s="44"/>
       <c r="C52" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D52" s="147" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" s="147"/>
+      <c r="F52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="132" t="s">
         <v>189</v>
       </c>
-      <c r="D52" s="156" t="s">
-        <v>190</v>
-      </c>
-      <c r="E52" s="156"/>
-      <c r="F52" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G52" s="8"/>
-      <c r="H52" s="148" t="s">
-        <v>191</v>
-      </c>
-      <c r="I52" s="148"/>
+      <c r="I52" s="132"/>
       <c r="J52" s="15"/>
       <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A53" s="135"/>
+      <c r="A53" s="163"/>
       <c r="B53" s="44"/>
       <c r="C53" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D53" s="132" t="s">
+        <v>191</v>
+      </c>
+      <c r="E53" s="132"/>
+      <c r="F53" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G53" s="9"/>
+      <c r="H53" s="132" t="s">
         <v>192</v>
       </c>
-      <c r="D53" s="148" t="s">
-        <v>193</v>
-      </c>
-      <c r="E53" s="148"/>
-      <c r="F53" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="148" t="s">
-        <v>194</v>
-      </c>
-      <c r="I53" s="148"/>
+      <c r="I53" s="132"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A54" s="135"/>
+      <c r="A54" s="163"/>
       <c r="B54" s="44"/>
       <c r="C54" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D54" s="132" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="132"/>
+      <c r="F54" s="132" t="s">
         <v>195</v>
       </c>
-      <c r="D54" s="148" t="s">
+      <c r="G54" s="132"/>
+      <c r="H54" s="132" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="148"/>
-      <c r="F54" s="148" t="s">
-        <v>197</v>
-      </c>
-      <c r="G54" s="148"/>
-      <c r="H54" s="148" t="s">
-        <v>198</v>
-      </c>
-      <c r="I54" s="148"/>
+      <c r="I54" s="132"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A55" s="135"/>
+      <c r="A55" s="163"/>
       <c r="B55" s="44"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="154" t="s">
-        <v>199</v>
-      </c>
-      <c r="E55" s="154"/>
-      <c r="F55" s="8"/>
+      <c r="D55" s="140" t="s">
+        <v>197</v>
+      </c>
+      <c r="E55" s="140"/>
+      <c r="F55" s="128" t="s">
+        <v>506</v>
+      </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -4026,15 +4049,15 @@
       <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A56" s="135"/>
+      <c r="A56" s="163"/>
       <c r="B56" s="44"/>
       <c r="C56" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D56" s="148" t="s">
-        <v>201</v>
-      </c>
-      <c r="E56" s="148"/>
+        <v>198</v>
+      </c>
+      <c r="D56" s="132" t="s">
+        <v>199</v>
+      </c>
+      <c r="E56" s="132"/>
       <c r="F56" s="18"/>
       <c r="G56" s="8"/>
       <c r="H56" s="9"/>
@@ -4056,362 +4079,362 @@
       <c r="K57" s="26"/>
     </row>
     <row r="58" spans="1:11" ht="25.5">
-      <c r="A58" s="132" t="s">
+      <c r="A58" s="160" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>204</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
-      <c r="F58" s="145" t="s">
-        <v>77</v>
+      <c r="F58" s="172" t="s">
+        <v>76</v>
       </c>
       <c r="G58" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="I58" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="H58" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="J58" s="162" t="s">
+      <c r="J58" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="K58" s="147"/>
+      <c r="K58" s="139"/>
     </row>
     <row r="59" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A59" s="133"/>
+      <c r="A59" s="161"/>
       <c r="B59" s="8"/>
       <c r="C59" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="163" t="s">
-        <v>208</v>
-      </c>
-      <c r="E59" s="163"/>
-      <c r="F59" s="139"/>
+        <v>78</v>
+      </c>
+      <c r="D59" s="141" t="s">
+        <v>206</v>
+      </c>
+      <c r="E59" s="141"/>
+      <c r="F59" s="167"/>
       <c r="G59" s="109"/>
       <c r="H59" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A60" s="133"/>
+      <c r="A60" s="161"/>
       <c r="B60" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D60" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E60" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F60" s="139"/>
+      <c r="F60" s="167"/>
       <c r="G60" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H60" s="109"/>
       <c r="I60" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J60" s="159" t="s">
+      <c r="J60" s="150" t="s">
+        <v>209</v>
+      </c>
+      <c r="K60" s="151"/>
+    </row>
+    <row r="61" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A61" s="161"/>
+      <c r="B61" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61" s="167"/>
+      <c r="G61" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I61" s="46" t="s">
         <v>211</v>
-      </c>
-      <c r="K60" s="160"/>
-    </row>
-    <row r="61" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A61" s="133"/>
-      <c r="B61" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F61" s="139"/>
-      <c r="G61" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="I61" s="46" t="s">
-        <v>213</v>
       </c>
       <c r="J61" s="47"/>
       <c r="K61" s="24"/>
     </row>
     <row r="62" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A62" s="133"/>
+      <c r="A62" s="161"/>
       <c r="B62" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D62" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F62" s="167"/>
+      <c r="G62" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="H62" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="I62" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="F62" s="139"/>
-      <c r="G62" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="J62" s="47"/>
       <c r="K62" s="24"/>
     </row>
     <row r="63" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A63" s="133"/>
+      <c r="A63" s="161"/>
       <c r="B63" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C63" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E63" s="22"/>
+      <c r="F63" s="167"/>
+      <c r="G63" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="140" t="s">
         <v>219</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E63" s="22"/>
-      <c r="F63" s="139"/>
-      <c r="G63" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="H63" s="154" t="s">
-        <v>222</v>
-      </c>
-      <c r="I63" s="154"/>
+      <c r="I63" s="140"/>
       <c r="J63" s="47"/>
       <c r="K63" s="24"/>
     </row>
     <row r="64" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A64" s="133"/>
+      <c r="A64" s="161"/>
       <c r="B64" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C64" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F64" s="167"/>
+      <c r="G64" s="147" t="s">
+        <v>222</v>
+      </c>
+      <c r="H64" s="147"/>
+      <c r="I64" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F64" s="139"/>
-      <c r="G64" s="156" t="s">
-        <v>225</v>
-      </c>
-      <c r="H64" s="156"/>
-      <c r="I64" s="8" t="s">
-        <v>226</v>
       </c>
       <c r="J64" s="47"/>
       <c r="K64" s="24"/>
     </row>
     <row r="65" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A65" s="133"/>
+      <c r="A65" s="161"/>
       <c r="B65" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="F65" s="167"/>
+      <c r="G65" s="147" t="s">
         <v>228</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="F65" s="139"/>
-      <c r="G65" s="156" t="s">
-        <v>231</v>
-      </c>
-      <c r="H65" s="156"/>
+      <c r="H65" s="147"/>
       <c r="I65" s="9"/>
       <c r="J65" s="47"/>
       <c r="K65" s="24"/>
     </row>
     <row r="66" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A66" s="133"/>
+      <c r="A66" s="161"/>
       <c r="B66" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="F66" s="167"/>
+      <c r="G66" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F66" s="139"/>
-      <c r="G66" s="8" t="s">
-        <v>236</v>
-      </c>
       <c r="H66" s="40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I66" s="48"/>
       <c r="J66" s="47"/>
       <c r="K66" s="24"/>
     </row>
     <row r="67" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A67" s="133"/>
+      <c r="A67" s="161"/>
       <c r="B67" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F67" s="167"/>
+      <c r="G67" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="C67" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="8" t="s">
+      <c r="H67" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="F67" s="139"/>
-      <c r="G67" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>241</v>
       </c>
       <c r="I67" s="48"/>
       <c r="J67" s="47"/>
       <c r="K67" s="24"/>
     </row>
     <row r="68" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A68" s="133"/>
+      <c r="A68" s="161"/>
       <c r="B68" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68" s="168"/>
+      <c r="G68" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="H68" s="138" t="s">
         <v>243</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="140"/>
-      <c r="G68" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="H68" s="146" t="s">
-        <v>246</v>
-      </c>
-      <c r="I68" s="147"/>
+      <c r="I68" s="139"/>
       <c r="J68" s="47"/>
       <c r="K68" s="24"/>
     </row>
     <row r="69" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A69" s="133"/>
+      <c r="A69" s="161"/>
       <c r="B69" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E69" s="9"/>
       <c r="F69" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G69" s="18"/>
-      <c r="H69" s="148"/>
-      <c r="I69" s="148"/>
+      <c r="H69" s="132"/>
+      <c r="I69" s="132"/>
       <c r="J69" s="47"/>
       <c r="K69" s="24"/>
     </row>
     <row r="70" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A70" s="133"/>
+      <c r="A70" s="161"/>
       <c r="B70" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C70" s="109"/>
-      <c r="D70" s="148" t="s">
-        <v>252</v>
-      </c>
-      <c r="E70" s="148"/>
+      <c r="D70" s="132" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" s="132"/>
       <c r="F70" s="46"/>
       <c r="G70" s="18"/>
-      <c r="H70" s="148" t="s">
-        <v>253</v>
-      </c>
-      <c r="I70" s="148"/>
+      <c r="H70" s="132" t="s">
+        <v>250</v>
+      </c>
+      <c r="I70" s="132"/>
       <c r="J70" s="47"/>
       <c r="K70" s="24"/>
     </row>
     <row r="71" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A71" s="133"/>
+      <c r="A71" s="161"/>
       <c r="B71" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C71" s="14"/>
-      <c r="D71" s="161" t="s">
-        <v>255</v>
-      </c>
-      <c r="E71" s="161"/>
+      <c r="D71" s="142" t="s">
+        <v>252</v>
+      </c>
+      <c r="E71" s="142"/>
       <c r="F71" s="16"/>
       <c r="G71" s="49"/>
-      <c r="H71" s="148" t="s">
-        <v>256</v>
-      </c>
-      <c r="I71" s="148"/>
+      <c r="H71" s="132" t="s">
+        <v>253</v>
+      </c>
+      <c r="I71" s="132"/>
       <c r="J71" s="47"/>
       <c r="K71" s="24"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A72" s="133"/>
+      <c r="A72" s="161"/>
       <c r="B72" s="21"/>
       <c r="C72" s="14"/>
-      <c r="D72" s="148" t="s">
-        <v>257</v>
-      </c>
-      <c r="E72" s="148"/>
+      <c r="D72" s="132" t="s">
+        <v>254</v>
+      </c>
+      <c r="E72" s="132"/>
       <c r="F72" s="50"/>
       <c r="G72" s="9"/>
-      <c r="H72" s="148" t="s">
-        <v>258</v>
-      </c>
-      <c r="I72" s="148"/>
+      <c r="H72" s="132" t="s">
+        <v>255</v>
+      </c>
+      <c r="I72" s="132"/>
       <c r="J72" s="47"/>
       <c r="K72" s="24"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="133"/>
+      <c r="A73" s="161"/>
       <c r="B73" s="21"/>
       <c r="C73" s="14"/>
-      <c r="D73" s="146" t="s">
-        <v>259</v>
-      </c>
-      <c r="E73" s="147"/>
+      <c r="D73" s="138" t="s">
+        <v>256</v>
+      </c>
+      <c r="E73" s="139"/>
       <c r="F73" s="50"/>
       <c r="G73" s="9"/>
       <c r="H73" s="18"/>
@@ -4420,7 +4443,7 @@
       <c r="K73" s="24"/>
     </row>
     <row r="74" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A74" s="133"/>
+      <c r="A74" s="161"/>
       <c r="B74" s="8"/>
       <c r="C74" s="14"/>
       <c r="D74" s="48"/>
@@ -4433,7 +4456,7 @@
       <c r="K74" s="24"/>
     </row>
     <row r="75" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A75" s="133"/>
+      <c r="A75" s="161"/>
       <c r="B75" s="8"/>
       <c r="C75" s="14"/>
       <c r="D75" s="48"/>
@@ -4459,204 +4482,204 @@
       <c r="K76" s="55"/>
     </row>
     <row r="77" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A77" s="136" t="s">
-        <v>260</v>
+      <c r="A77" s="164" t="s">
+        <v>257</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D77" s="56"/>
       <c r="E77" s="56"/>
       <c r="F77" s="57"/>
       <c r="G77" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="I77" s="58" t="s">
+        <v>261</v>
+      </c>
+      <c r="J77" s="148" t="s">
+        <v>19</v>
+      </c>
+      <c r="K77" s="149"/>
+    </row>
+    <row r="78" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A78" s="165"/>
+      <c r="B78" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="E78" s="59" t="s">
         <v>263</v>
-      </c>
-      <c r="I77" s="58" t="s">
-        <v>264</v>
-      </c>
-      <c r="J77" s="157" t="s">
-        <v>19</v>
-      </c>
-      <c r="K77" s="158"/>
-    </row>
-    <row r="78" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A78" s="137"/>
-      <c r="B78" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="D78" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="E78" s="59" t="s">
-        <v>266</v>
       </c>
       <c r="F78" s="113"/>
       <c r="G78" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H78" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="H78" s="42" t="s">
-        <v>88</v>
-      </c>
       <c r="I78" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="J78" s="150" t="s">
+        <v>265</v>
+      </c>
+      <c r="K78" s="151"/>
+    </row>
+    <row r="79" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A79" s="165"/>
+      <c r="B79" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E79" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="J78" s="159" t="s">
-        <v>268</v>
-      </c>
-      <c r="K78" s="160"/>
-    </row>
-    <row r="79" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A79" s="137"/>
-      <c r="B79" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>270</v>
       </c>
       <c r="F79" s="60"/>
       <c r="G79" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I79" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="J79" s="150" t="s">
+        <v>269</v>
+      </c>
+      <c r="K79" s="151"/>
+    </row>
+    <row r="80" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A80" s="165"/>
+      <c r="B80" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="C80" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E80" s="8" t="s">
         <v>271</v>
-      </c>
-      <c r="J79" s="159" t="s">
-        <v>272</v>
-      </c>
-      <c r="K79" s="160"/>
-    </row>
-    <row r="80" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A80" s="137"/>
-      <c r="B80" s="42" t="s">
-        <v>273</v>
-      </c>
-      <c r="C80" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>274</v>
       </c>
       <c r="F80" s="60"/>
       <c r="G80" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I80" s="42" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J80" s="114"/>
       <c r="K80" s="115"/>
     </row>
     <row r="81" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A81" s="137"/>
+      <c r="A81" s="165"/>
       <c r="B81" s="42" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C81" s="42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D81" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E81" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E81" s="11" t="s">
-        <v>162</v>
-      </c>
       <c r="F81" s="60" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="H81" s="148"/>
-      <c r="I81" s="148"/>
+        <v>275</v>
+      </c>
+      <c r="H81" s="132"/>
+      <c r="I81" s="132"/>
       <c r="J81" s="114"/>
       <c r="K81" s="115"/>
     </row>
     <row r="82" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A82" s="137"/>
+      <c r="A82" s="165"/>
       <c r="B82" s="42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C82" s="42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F82" s="60"/>
       <c r="G82" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H82" s="148" t="s">
-        <v>281</v>
-      </c>
-      <c r="I82" s="148"/>
+        <v>106</v>
+      </c>
+      <c r="H82" s="132" t="s">
+        <v>278</v>
+      </c>
+      <c r="I82" s="132"/>
       <c r="J82" s="114"/>
       <c r="K82" s="115"/>
     </row>
     <row r="83" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A83" s="137"/>
+      <c r="A83" s="165"/>
       <c r="B83" s="42" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C83" s="42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F83" s="60"/>
       <c r="G83" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="H83" s="148"/>
-      <c r="I83" s="148"/>
+        <v>282</v>
+      </c>
+      <c r="H83" s="132"/>
+      <c r="I83" s="132"/>
       <c r="J83" s="114"/>
       <c r="K83" s="115"/>
     </row>
     <row r="84" spans="1:11" ht="18" customHeight="1">
-      <c r="A84" s="137"/>
+      <c r="A84" s="165"/>
       <c r="B84" s="42" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C84" s="42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F84" s="60"/>
       <c r="G84" s="13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H84" s="16"/>
       <c r="I84" s="8"/>
@@ -4664,20 +4687,20 @@
       <c r="K84" s="115"/>
     </row>
     <row r="85" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A85" s="137"/>
+      <c r="A85" s="165"/>
       <c r="B85" s="42" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C85" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="D85" s="154" t="s">
-        <v>290</v>
-      </c>
-      <c r="E85" s="154"/>
+        <v>120</v>
+      </c>
+      <c r="D85" s="140" t="s">
+        <v>287</v>
+      </c>
+      <c r="E85" s="140"/>
       <c r="F85" s="60"/>
       <c r="G85" s="62" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H85" s="8"/>
       <c r="I85" s="8"/>
@@ -4685,99 +4708,99 @@
       <c r="K85" s="115"/>
     </row>
     <row r="86" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A86" s="137"/>
+      <c r="A86" s="165"/>
       <c r="B86" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="C86" s="42" t="s">
+        <v>290</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E86" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="C86" s="42" t="s">
+      <c r="F86" s="60"/>
+      <c r="G86" s="132" t="s">
         <v>293</v>
       </c>
-      <c r="D86" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="F86" s="60"/>
-      <c r="G86" s="148" t="s">
-        <v>296</v>
-      </c>
-      <c r="H86" s="148"/>
+      <c r="H86" s="132"/>
       <c r="I86" s="8"/>
       <c r="J86" s="114"/>
       <c r="K86" s="115"/>
     </row>
     <row r="87" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A87" s="137"/>
+      <c r="A87" s="165"/>
       <c r="B87" s="42" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C87" s="42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E87" s="109"/>
       <c r="F87" s="60"/>
-      <c r="G87" s="154" t="s">
-        <v>299</v>
-      </c>
-      <c r="H87" s="154"/>
+      <c r="G87" s="140" t="s">
+        <v>296</v>
+      </c>
+      <c r="H87" s="140"/>
       <c r="I87" s="8"/>
       <c r="J87" s="114"/>
       <c r="K87" s="115"/>
     </row>
     <row r="88" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A88" s="137"/>
+      <c r="A88" s="165"/>
       <c r="B88" s="116" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C88" s="42" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F88" s="60"/>
-      <c r="G88" s="156" t="s">
-        <v>303</v>
-      </c>
-      <c r="H88" s="156"/>
+      <c r="G88" s="147" t="s">
+        <v>300</v>
+      </c>
+      <c r="H88" s="147"/>
       <c r="I88" s="8"/>
       <c r="J88" s="114"/>
       <c r="K88" s="115"/>
     </row>
     <row r="89" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A89" s="137"/>
+      <c r="A89" s="165"/>
       <c r="B89" s="117"/>
       <c r="C89" s="42" t="s">
-        <v>304</v>
-      </c>
-      <c r="D89" s="148" t="s">
-        <v>305</v>
-      </c>
-      <c r="E89" s="148"/>
+        <v>301</v>
+      </c>
+      <c r="D89" s="132" t="s">
+        <v>302</v>
+      </c>
+      <c r="E89" s="132"/>
       <c r="F89" s="60"/>
-      <c r="G89" s="156" t="s">
-        <v>306</v>
-      </c>
-      <c r="H89" s="156"/>
+      <c r="G89" s="147" t="s">
+        <v>303</v>
+      </c>
+      <c r="H89" s="147"/>
       <c r="I89" s="8"/>
       <c r="J89" s="114"/>
       <c r="K89" s="115"/>
     </row>
     <row r="90" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A90" s="137"/>
+      <c r="A90" s="165"/>
       <c r="B90" s="111"/>
       <c r="C90" s="118" t="s">
-        <v>307</v>
-      </c>
-      <c r="D90" s="148" t="s">
-        <v>308</v>
-      </c>
-      <c r="E90" s="148"/>
+        <v>304</v>
+      </c>
+      <c r="D90" s="132" t="s">
+        <v>305</v>
+      </c>
+      <c r="E90" s="132"/>
       <c r="F90" s="60"/>
       <c r="G90" s="42"/>
       <c r="H90" s="16"/>
@@ -4786,13 +4809,13 @@
       <c r="K90" s="115"/>
     </row>
     <row r="91" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A91" s="137"/>
+      <c r="A91" s="165"/>
       <c r="B91" s="111"/>
       <c r="C91" s="118" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D91" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E91" s="155"/>
       <c r="F91" s="113"/>
@@ -4803,11 +4826,11 @@
       <c r="K91" s="115"/>
     </row>
     <row r="92" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A92" s="137"/>
+      <c r="A92" s="165"/>
       <c r="B92" s="120"/>
       <c r="C92" s="117"/>
       <c r="D92" s="155" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E92" s="155"/>
       <c r="F92" s="113"/>
@@ -4818,13 +4841,13 @@
       <c r="K92" s="115"/>
     </row>
     <row r="93" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A93" s="137"/>
+      <c r="A93" s="165"/>
       <c r="B93" s="122"/>
       <c r="C93" s="117"/>
-      <c r="D93" s="128" t="s">
-        <v>502</v>
-      </c>
-      <c r="E93" s="128"/>
+      <c r="D93" s="156" t="s">
+        <v>499</v>
+      </c>
+      <c r="E93" s="156"/>
       <c r="F93" s="113"/>
       <c r="G93" s="119"/>
       <c r="H93" s="110"/>
@@ -4833,7 +4856,7 @@
       <c r="K93" s="115"/>
     </row>
     <row r="94" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A94" s="137"/>
+      <c r="A94" s="165"/>
       <c r="B94" s="120"/>
       <c r="C94" s="117"/>
       <c r="D94" s="123"/>
@@ -4859,39 +4882,39 @@
       <c r="K95" s="26"/>
     </row>
     <row r="96" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A96" s="136" t="s">
-        <v>312</v>
+      <c r="A96" s="164" t="s">
+        <v>309</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D96" s="56"/>
       <c r="E96" s="56"/>
-      <c r="F96" s="150" t="s">
-        <v>315</v>
-      </c>
-      <c r="G96" s="151"/>
+      <c r="F96" s="173" t="s">
+        <v>312</v>
+      </c>
+      <c r="G96" s="174"/>
       <c r="H96" s="64"/>
       <c r="I96" s="152"/>
       <c r="J96" s="153"/>
       <c r="K96" s="65"/>
     </row>
     <row r="97" spans="1:11" ht="30" customHeight="1">
-      <c r="A97" s="137"/>
+      <c r="A97" s="165"/>
       <c r="B97" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F97" s="21"/>
       <c r="G97" s="66"/>
@@ -4901,15 +4924,15 @@
       <c r="K97" s="65"/>
     </row>
     <row r="98" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A98" s="137"/>
+      <c r="A98" s="165"/>
       <c r="B98" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="21"/>
@@ -4920,15 +4943,15 @@
       <c r="K98" s="65"/>
     </row>
     <row r="99" spans="1:11" ht="30" customHeight="1">
-      <c r="A99" s="137"/>
+      <c r="A99" s="165"/>
       <c r="B99" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="21"/>
@@ -4939,12 +4962,12 @@
       <c r="K99" s="65"/>
     </row>
     <row r="100" spans="1:11" ht="30" customHeight="1">
-      <c r="A100" s="137"/>
+      <c r="A100" s="165"/>
       <c r="B100" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="16"/>
@@ -4956,17 +4979,17 @@
       <c r="K100" s="65"/>
     </row>
     <row r="101" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A101" s="137"/>
+      <c r="A101" s="165"/>
       <c r="B101" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="D101" s="144" t="s">
-        <v>329</v>
-      </c>
-      <c r="E101" s="144"/>
+        <v>325</v>
+      </c>
+      <c r="D101" s="154" t="s">
+        <v>326</v>
+      </c>
+      <c r="E101" s="154"/>
       <c r="F101" s="21"/>
       <c r="G101" s="30"/>
       <c r="H101" s="64"/>
@@ -4975,14 +4998,14 @@
       <c r="K101" s="65"/>
     </row>
     <row r="102" spans="1:11" ht="27" customHeight="1">
-      <c r="A102" s="137"/>
+      <c r="A102" s="165"/>
       <c r="C102" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D102" s="154" t="s">
-        <v>331</v>
-      </c>
-      <c r="E102" s="154"/>
+        <v>327</v>
+      </c>
+      <c r="D102" s="140" t="s">
+        <v>328</v>
+      </c>
+      <c r="E102" s="140"/>
       <c r="F102" s="15"/>
       <c r="G102" s="8"/>
       <c r="H102" s="64"/>
@@ -4991,14 +5014,14 @@
       <c r="K102" s="65"/>
     </row>
     <row r="103" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A103" s="137"/>
+      <c r="A103" s="165"/>
       <c r="C103" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="D103" s="148" t="s">
-        <v>333</v>
-      </c>
-      <c r="E103" s="148"/>
+        <v>329</v>
+      </c>
+      <c r="D103" s="132" t="s">
+        <v>330</v>
+      </c>
+      <c r="E103" s="132"/>
       <c r="F103" s="15"/>
       <c r="G103" s="8"/>
       <c r="H103" s="6"/>
@@ -5007,12 +5030,12 @@
       <c r="K103" s="67"/>
     </row>
     <row r="104" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A104" s="137"/>
+      <c r="A104" s="165"/>
       <c r="B104" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D104" s="22"/>
       <c r="E104" s="22"/>
@@ -5024,15 +5047,15 @@
       <c r="K104" s="67"/>
     </row>
     <row r="105" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A105" s="137"/>
+      <c r="A105" s="165"/>
       <c r="B105" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D105" s="155" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E105" s="155"/>
       <c r="F105" s="15"/>
@@ -5043,13 +5066,13 @@
       <c r="K105" s="67"/>
     </row>
     <row r="106" spans="1:11" ht="15" customHeight="1">
-      <c r="A106" s="137"/>
+      <c r="A106" s="165"/>
       <c r="B106" s="9"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="146" t="s">
-        <v>339</v>
-      </c>
-      <c r="E106" s="147"/>
+      <c r="D106" s="138" t="s">
+        <v>336</v>
+      </c>
+      <c r="E106" s="139"/>
       <c r="F106" s="15"/>
       <c r="G106" s="8"/>
       <c r="H106" s="6"/>
@@ -5058,13 +5081,13 @@
       <c r="K106" s="67"/>
     </row>
     <row r="107" spans="1:11" ht="15" customHeight="1">
-      <c r="A107" s="137"/>
+      <c r="A107" s="165"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="146" t="s">
-        <v>340</v>
-      </c>
-      <c r="E107" s="147"/>
+      <c r="D107" s="138" t="s">
+        <v>337</v>
+      </c>
+      <c r="E107" s="139"/>
       <c r="F107" s="15"/>
       <c r="G107" s="8"/>
       <c r="H107" s="6"/>
@@ -5073,11 +5096,11 @@
       <c r="K107" s="67"/>
     </row>
     <row r="108" spans="1:11" ht="15" customHeight="1">
-      <c r="A108" s="137"/>
-      <c r="B108" s="146" t="s">
+      <c r="A108" s="165"/>
+      <c r="B108" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="C108" s="147"/>
+      <c r="C108" s="139"/>
       <c r="F108" s="15"/>
       <c r="G108" s="8"/>
       <c r="H108" s="6"/>
@@ -5086,15 +5109,15 @@
       <c r="K108" s="67"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="137"/>
-      <c r="B109" s="148" t="s">
-        <v>341</v>
-      </c>
-      <c r="C109" s="148"/>
-      <c r="D109" s="146" t="s">
-        <v>342</v>
-      </c>
-      <c r="E109" s="147"/>
+      <c r="A109" s="165"/>
+      <c r="B109" s="132" t="s">
+        <v>338</v>
+      </c>
+      <c r="C109" s="132"/>
+      <c r="D109" s="138" t="s">
+        <v>339</v>
+      </c>
+      <c r="E109" s="139"/>
       <c r="F109" s="15"/>
       <c r="G109" s="8"/>
       <c r="H109" s="6"/>
@@ -5103,11 +5126,11 @@
       <c r="K109" s="67"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="137"/>
-      <c r="B110" s="148" t="s">
-        <v>343</v>
-      </c>
-      <c r="C110" s="148"/>
+      <c r="A110" s="165"/>
+      <c r="B110" s="132" t="s">
+        <v>340</v>
+      </c>
+      <c r="C110" s="132"/>
       <c r="D110" s="9"/>
       <c r="E110" s="8"/>
       <c r="F110" s="15"/>
@@ -5118,11 +5141,11 @@
       <c r="K110" s="67"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="137"/>
-      <c r="B111" s="148" t="s">
-        <v>344</v>
-      </c>
-      <c r="C111" s="148"/>
+      <c r="A111" s="165"/>
+      <c r="B111" s="132" t="s">
+        <v>341</v>
+      </c>
+      <c r="C111" s="132"/>
       <c r="D111" s="33"/>
       <c r="E111" s="29"/>
       <c r="F111" s="68"/>
@@ -5133,14 +5156,14 @@
       <c r="K111" s="67"/>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" s="137"/>
-      <c r="B112" s="149" t="s">
-        <v>508</v>
-      </c>
-      <c r="C112" s="149"/>
+      <c r="A112" s="165"/>
+      <c r="B112" s="133" t="s">
+        <v>505</v>
+      </c>
+      <c r="C112" s="133"/>
       <c r="D112" s="56"/>
       <c r="E112" s="69" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F112" s="68"/>
       <c r="G112" s="27"/>
@@ -5150,11 +5173,11 @@
       <c r="K112" s="67"/>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" s="137"/>
-      <c r="B113" s="148" t="s">
-        <v>346</v>
-      </c>
-      <c r="C113" s="148"/>
+      <c r="A113" s="165"/>
+      <c r="B113" s="132" t="s">
+        <v>343</v>
+      </c>
+      <c r="C113" s="132"/>
       <c r="D113" s="56"/>
       <c r="E113" s="69"/>
       <c r="F113" s="68"/>
@@ -5165,11 +5188,11 @@
       <c r="K113" s="67"/>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" s="137"/>
-      <c r="B114" s="149" t="s">
-        <v>505</v>
-      </c>
-      <c r="C114" s="149"/>
+      <c r="A114" s="165"/>
+      <c r="B114" s="133" t="s">
+        <v>502</v>
+      </c>
+      <c r="C114" s="133"/>
       <c r="D114" s="56"/>
       <c r="E114" s="69"/>
       <c r="F114" s="68"/>
@@ -5180,11 +5203,11 @@
       <c r="K114" s="67"/>
     </row>
     <row r="115" spans="1:11" ht="15" customHeight="1">
-      <c r="A115" s="137"/>
-      <c r="B115" s="149" t="s">
-        <v>506</v>
-      </c>
-      <c r="C115" s="149"/>
+      <c r="A115" s="165"/>
+      <c r="B115" s="133" t="s">
+        <v>503</v>
+      </c>
+      <c r="C115" s="133"/>
       <c r="D115" s="56"/>
       <c r="E115" s="69"/>
       <c r="F115" s="68"/>
@@ -5195,11 +5218,11 @@
       <c r="K115" s="67"/>
     </row>
     <row r="116" spans="1:11">
-      <c r="A116" s="137"/>
-      <c r="B116" s="128" t="s">
-        <v>507</v>
-      </c>
-      <c r="C116" s="128"/>
+      <c r="A116" s="165"/>
+      <c r="B116" s="156" t="s">
+        <v>504</v>
+      </c>
+      <c r="C116" s="156"/>
       <c r="D116" s="56"/>
       <c r="E116" s="69"/>
       <c r="F116" s="68"/>
@@ -5237,542 +5260,542 @@
     </row>
     <row r="119" spans="1:11">
       <c r="B119" s="75" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C119" s="75" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E119" s="76" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F119" s="76" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H119" s="76" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I119" s="76" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="B120" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C120" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="E120" s="77" t="s">
+        <v>348</v>
+      </c>
+      <c r="F120" s="78" t="s">
         <v>349</v>
       </c>
-      <c r="C120" s="33" t="s">
+      <c r="H120" s="79" t="s">
         <v>350</v>
       </c>
-      <c r="E120" s="77" t="s">
+      <c r="I120" s="80" t="s">
         <v>351</v>
-      </c>
-      <c r="F120" s="78" t="s">
-        <v>352</v>
-      </c>
-      <c r="H120" s="79" t="s">
-        <v>353</v>
-      </c>
-      <c r="I120" s="80" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="B121" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="C121" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="E121" s="81" t="s">
+        <v>354</v>
+      </c>
+      <c r="F121" s="78" t="s">
         <v>355</v>
       </c>
-      <c r="C121" s="33" t="s">
+      <c r="H121" s="82" t="s">
+        <v>350</v>
+      </c>
+      <c r="I121" s="83" t="s">
         <v>356</v>
-      </c>
-      <c r="E121" s="81" t="s">
-        <v>357</v>
-      </c>
-      <c r="F121" s="78" t="s">
-        <v>358</v>
-      </c>
-      <c r="H121" s="82" t="s">
-        <v>353</v>
-      </c>
-      <c r="I121" s="83" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="B122" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="E122" s="77" t="s">
+        <v>359</v>
+      </c>
+      <c r="F122" s="78" t="s">
         <v>360</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="H122" s="82" t="s">
         <v>361</v>
       </c>
-      <c r="E122" s="77" t="s">
+      <c r="I122" s="83" t="s">
         <v>362</v>
-      </c>
-      <c r="F122" s="78" t="s">
-        <v>363</v>
-      </c>
-      <c r="H122" s="82" t="s">
-        <v>364</v>
-      </c>
-      <c r="I122" s="83" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="B123" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="C123" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="E123" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="F123" s="78" t="s">
         <v>366</v>
       </c>
-      <c r="C123" s="33" t="s">
+      <c r="H123" s="82" t="s">
         <v>367</v>
       </c>
-      <c r="E123" s="77" t="s">
+      <c r="I123" s="83" t="s">
         <v>368</v>
-      </c>
-      <c r="F123" s="78" t="s">
-        <v>369</v>
-      </c>
-      <c r="H123" s="82" t="s">
-        <v>370</v>
-      </c>
-      <c r="I123" s="83" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="B124" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="C124" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="E124" s="77" t="s">
+        <v>371</v>
+      </c>
+      <c r="F124" s="78" t="s">
         <v>372</v>
-      </c>
-      <c r="C124" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="E124" s="77" t="s">
-        <v>374</v>
-      </c>
-      <c r="F124" s="78" t="s">
-        <v>375</v>
       </c>
       <c r="H124" s="84"/>
       <c r="I124" s="85" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="B125" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="C125" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="E125" s="77" t="s">
+        <v>376</v>
+      </c>
+      <c r="F125" s="78" t="s">
         <v>377</v>
       </c>
-      <c r="C125" s="33" t="s">
+      <c r="H125" s="86" t="s">
         <v>378</v>
       </c>
-      <c r="E125" s="77" t="s">
+      <c r="I125" s="87" t="s">
         <v>379</v>
-      </c>
-      <c r="F125" s="78" t="s">
-        <v>380</v>
-      </c>
-      <c r="H125" s="86" t="s">
-        <v>381</v>
-      </c>
-      <c r="I125" s="87" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="B126" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="C126" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="E126" s="77" t="s">
+        <v>382</v>
+      </c>
+      <c r="F126" s="78" t="s">
         <v>383</v>
       </c>
-      <c r="C126" s="33" t="s">
+      <c r="H126" s="86" t="s">
         <v>384</v>
       </c>
-      <c r="E126" s="77" t="s">
+      <c r="I126" s="87" t="s">
         <v>385</v>
-      </c>
-      <c r="F126" s="78" t="s">
-        <v>386</v>
-      </c>
-      <c r="H126" s="86" t="s">
-        <v>387</v>
-      </c>
-      <c r="I126" s="87" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="B127" s="33" t="s">
+        <v>386</v>
+      </c>
+      <c r="C127" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="E127" s="77" t="s">
+        <v>388</v>
+      </c>
+      <c r="F127" s="78" t="s">
         <v>389</v>
-      </c>
-      <c r="C127" s="33" t="s">
-        <v>390</v>
-      </c>
-      <c r="E127" s="77" t="s">
-        <v>391</v>
-      </c>
-      <c r="F127" s="78" t="s">
-        <v>392</v>
       </c>
       <c r="H127" s="88"/>
       <c r="I127" s="89" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="B128" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="C128" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="E128" s="77" t="s">
+        <v>393</v>
+      </c>
+      <c r="F128" s="78" t="s">
         <v>394</v>
-      </c>
-      <c r="C128" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="E128" s="77" t="s">
-        <v>396</v>
-      </c>
-      <c r="F128" s="78" t="s">
-        <v>397</v>
       </c>
       <c r="H128" s="90"/>
       <c r="I128" s="83" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="2:9">
       <c r="B129" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="C129" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="E129" s="77" t="s">
+        <v>398</v>
+      </c>
+      <c r="F129" s="78" t="s">
         <v>399</v>
       </c>
-      <c r="C129" s="33" t="s">
+      <c r="H129" s="91" t="s">
         <v>400</v>
       </c>
-      <c r="E129" s="77" t="s">
+      <c r="I129" s="83" t="s">
         <v>401</v>
-      </c>
-      <c r="F129" s="78" t="s">
-        <v>402</v>
-      </c>
-      <c r="H129" s="91" t="s">
-        <v>403</v>
-      </c>
-      <c r="I129" s="83" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="130" spans="2:9">
       <c r="B130" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="C130" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="E130" s="77" t="s">
+        <v>404</v>
+      </c>
+      <c r="F130" s="78" t="s">
         <v>405</v>
       </c>
-      <c r="C130" s="33" t="s">
+      <c r="H130" s="91" t="s">
         <v>406</v>
       </c>
-      <c r="E130" s="77" t="s">
+      <c r="I130" s="83" t="s">
         <v>407</v>
-      </c>
-      <c r="F130" s="78" t="s">
-        <v>408</v>
-      </c>
-      <c r="H130" s="91" t="s">
-        <v>409</v>
-      </c>
-      <c r="I130" s="83" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="C131" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="E131" s="77" t="s">
+        <v>410</v>
+      </c>
+      <c r="F131" s="78" t="s">
         <v>411</v>
-      </c>
-      <c r="C131" s="33" t="s">
-        <v>412</v>
-      </c>
-      <c r="E131" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="F131" s="78" t="s">
-        <v>414</v>
       </c>
       <c r="H131" s="90"/>
       <c r="I131" s="83" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="132" spans="2:9">
       <c r="B132" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="C132" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="E132" s="77" t="s">
+        <v>415</v>
+      </c>
+      <c r="F132" s="78" t="s">
         <v>416</v>
       </c>
-      <c r="C132" s="33" t="s">
+      <c r="H132" s="92" t="s">
         <v>417</v>
       </c>
-      <c r="E132" s="77" t="s">
+      <c r="I132" s="93" t="s">
         <v>418</v>
-      </c>
-      <c r="F132" s="78" t="s">
-        <v>419</v>
-      </c>
-      <c r="H132" s="92" t="s">
-        <v>420</v>
-      </c>
-      <c r="I132" s="93" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="C133" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="E133" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="F133" s="78" t="s">
         <v>422</v>
       </c>
-      <c r="C133" s="33" t="s">
+      <c r="H133" s="92" t="s">
         <v>423</v>
       </c>
-      <c r="E133" s="77" t="s">
+      <c r="I133" s="93" t="s">
         <v>424</v>
-      </c>
-      <c r="F133" s="78" t="s">
-        <v>425</v>
-      </c>
-      <c r="H133" s="92" t="s">
-        <v>426</v>
-      </c>
-      <c r="I133" s="93" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="C134" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="E134" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="F134" s="78" t="s">
         <v>428</v>
       </c>
-      <c r="C134" s="33" t="s">
+      <c r="H134" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="E134" s="77" t="s">
+      <c r="I134" s="78" t="s">
         <v>430</v>
-      </c>
-      <c r="F134" s="78" t="s">
-        <v>431</v>
-      </c>
-      <c r="H134" s="33" t="s">
-        <v>432</v>
-      </c>
-      <c r="I134" s="78" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="C135" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="E135" s="77" t="s">
+        <v>433</v>
+      </c>
+      <c r="F135" s="78" t="s">
         <v>434</v>
       </c>
-      <c r="C135" s="33" t="s">
+      <c r="H135" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="E135" s="77" t="s">
+      <c r="I135" s="78" t="s">
         <v>436</v>
-      </c>
-      <c r="F135" s="78" t="s">
-        <v>437</v>
-      </c>
-      <c r="H135" s="33" t="s">
-        <v>438</v>
-      </c>
-      <c r="I135" s="78" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="33" t="s">
+        <v>437</v>
+      </c>
+      <c r="C136" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="E136" s="77" t="s">
+        <v>439</v>
+      </c>
+      <c r="F136" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="C136" s="33" t="s">
+      <c r="H136" s="33" t="s">
         <v>441</v>
       </c>
-      <c r="E136" s="77" t="s">
+      <c r="I136" s="78" t="s">
         <v>442</v>
-      </c>
-      <c r="F136" s="78" t="s">
-        <v>443</v>
-      </c>
-      <c r="H136" s="33" t="s">
-        <v>444</v>
-      </c>
-      <c r="I136" s="78" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="33" t="s">
+        <v>443</v>
+      </c>
+      <c r="C137" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="E137" s="77" t="s">
+        <v>445</v>
+      </c>
+      <c r="F137" s="78" t="s">
         <v>446</v>
       </c>
-      <c r="C137" s="33" t="s">
+      <c r="H137" s="77" t="s">
         <v>447</v>
       </c>
-      <c r="E137" s="77" t="s">
+      <c r="I137" s="56" t="s">
         <v>448</v>
-      </c>
-      <c r="F137" s="78" t="s">
-        <v>449</v>
-      </c>
-      <c r="H137" s="77" t="s">
-        <v>450</v>
-      </c>
-      <c r="I137" s="56" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="C138" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="E138" s="77" t="s">
+        <v>451</v>
+      </c>
+      <c r="F138" s="78" t="s">
         <v>452</v>
       </c>
-      <c r="C138" s="33" t="s">
+      <c r="H138" s="77" t="s">
         <v>453</v>
       </c>
-      <c r="E138" s="77" t="s">
+      <c r="I138" s="56" t="s">
         <v>454</v>
-      </c>
-      <c r="F138" s="78" t="s">
-        <v>455</v>
-      </c>
-      <c r="H138" s="77" t="s">
-        <v>456</v>
-      </c>
-      <c r="I138" s="56" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="94" t="s">
+        <v>455</v>
+      </c>
+      <c r="C139" s="94" t="s">
+        <v>456</v>
+      </c>
+      <c r="E139" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="F139" s="78" t="s">
         <v>458</v>
       </c>
-      <c r="C139" s="94" t="s">
+      <c r="H139" s="95" t="s">
         <v>459</v>
       </c>
-      <c r="E139" s="33" t="s">
+      <c r="I139" s="96" t="s">
         <v>460</v>
-      </c>
-      <c r="F139" s="78" t="s">
-        <v>461</v>
-      </c>
-      <c r="H139" s="95" t="s">
-        <v>462</v>
-      </c>
-      <c r="I139" s="96" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="140" spans="2:9">
       <c r="B140" s="97" t="s">
+        <v>461</v>
+      </c>
+      <c r="C140" s="98" t="s">
+        <v>462</v>
+      </c>
+      <c r="E140" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="F140" s="78" t="s">
         <v>464</v>
       </c>
-      <c r="C140" s="98" t="s">
+      <c r="H140" s="97" t="s">
         <v>465</v>
       </c>
-      <c r="E140" s="33" t="s">
+      <c r="I140" s="96" t="s">
         <v>466</v>
-      </c>
-      <c r="F140" s="78" t="s">
-        <v>467</v>
-      </c>
-      <c r="H140" s="97" t="s">
-        <v>468</v>
-      </c>
-      <c r="I140" s="96" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="141" spans="2:9">
       <c r="B141" s="97" t="s">
+        <v>467</v>
+      </c>
+      <c r="C141" s="98" t="s">
+        <v>468</v>
+      </c>
+      <c r="E141" s="33" t="s">
+        <v>469</v>
+      </c>
+      <c r="F141" s="78" t="s">
         <v>470</v>
       </c>
-      <c r="C141" s="98" t="s">
+      <c r="H141" s="95" t="s">
         <v>471</v>
       </c>
-      <c r="E141" s="33" t="s">
+      <c r="I141" s="96" t="s">
         <v>472</v>
-      </c>
-      <c r="F141" s="78" t="s">
-        <v>473</v>
-      </c>
-      <c r="H141" s="95" t="s">
-        <v>474</v>
-      </c>
-      <c r="I141" s="96" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="142" spans="2:9">
       <c r="B142" s="95" t="s">
+        <v>473</v>
+      </c>
+      <c r="C142" s="98" t="s">
+        <v>474</v>
+      </c>
+      <c r="E142" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="F142" s="78" t="s">
         <v>476</v>
       </c>
-      <c r="C142" s="98" t="s">
+      <c r="H142" s="99" t="s">
         <v>477</v>
       </c>
-      <c r="E142" s="33" t="s">
+      <c r="I142" s="100" t="s">
         <v>478</v>
-      </c>
-      <c r="F142" s="78" t="s">
-        <v>479</v>
-      </c>
-      <c r="H142" s="99" t="s">
-        <v>480</v>
-      </c>
-      <c r="I142" s="100" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="143" spans="2:9" ht="25.5" customHeight="1">
       <c r="B143" s="97" t="s">
+        <v>479</v>
+      </c>
+      <c r="C143" s="98" t="s">
+        <v>480</v>
+      </c>
+      <c r="E143" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="F143" s="78" t="s">
         <v>482</v>
       </c>
-      <c r="C143" s="98" t="s">
+      <c r="H143" s="99" t="s">
         <v>483</v>
       </c>
-      <c r="E143" s="33" t="s">
+      <c r="I143" s="99" t="s">
         <v>484</v>
-      </c>
-      <c r="F143" s="78" t="s">
-        <v>485</v>
-      </c>
-      <c r="H143" s="99" t="s">
-        <v>486</v>
-      </c>
-      <c r="I143" s="99" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="144" spans="2:9" ht="39" customHeight="1">
       <c r="B144" s="95" t="s">
+        <v>485</v>
+      </c>
+      <c r="C144" s="96" t="s">
+        <v>486</v>
+      </c>
+      <c r="E144" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="F144" s="78" t="s">
         <v>488</v>
       </c>
-      <c r="C144" s="96" t="s">
+      <c r="H144" s="99" t="s">
         <v>489</v>
       </c>
-      <c r="E144" s="33" t="s">
+      <c r="I144" s="99" t="s">
         <v>490</v>
-      </c>
-      <c r="F144" s="78" t="s">
-        <v>491</v>
-      </c>
-      <c r="H144" s="99" t="s">
-        <v>492</v>
-      </c>
-      <c r="I144" s="99" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="145" spans="2:9" ht="26.25" customHeight="1">
       <c r="B145" s="99" t="s">
+        <v>491</v>
+      </c>
+      <c r="C145" s="99" t="s">
+        <v>492</v>
+      </c>
+      <c r="E145" s="33" t="s">
+        <v>493</v>
+      </c>
+      <c r="F145" s="78" t="s">
         <v>494</v>
       </c>
-      <c r="C145" s="99" t="s">
+      <c r="H145" s="99" t="s">
         <v>495</v>
       </c>
-      <c r="E145" s="33" t="s">
+      <c r="I145" s="99" t="s">
         <v>496</v>
-      </c>
-      <c r="F145" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="H145" s="99" t="s">
-        <v>498</v>
-      </c>
-      <c r="I145" s="99" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="146" spans="2:9">
       <c r="H146" s="99" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="I146" s="99" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="147" spans="2:9">
@@ -5965,98 +5988,6 @@
     </row>
   </sheetData>
   <mergeCells count="116">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="D92:E92"/>
     <mergeCell ref="B116:C116"/>
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A22:A36"/>
@@ -6081,6 +6012,98 @@
     <mergeCell ref="F96:G96"/>
     <mergeCell ref="D72:E72"/>
     <mergeCell ref="D53:E53"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <pageMargins left="0.24" right="0.17" top="0.17" bottom="0.28000000000000003" header="0.17" footer="0.16"/>
   <pageSetup scale="60" orientation="landscape" r:id="rId1"/>
